--- a/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/CompromisedImmuneSystemCodes</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/CompromisedImmuneSystemCodes</t>
   </si>
   <si>
     <t>Version</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/branches/updated-examples/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
